--- a/sources/baek_step4.xlsx
+++ b/sources/baek_step4.xlsx
@@ -785,6 +785,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -827,6 +832,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -867,6 +877,11 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -6230,6 +6245,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -6255,6 +6275,11 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>hhhlmmmlm[!]</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
